--- a/Luban/Config/Datas/LevelRating.xlsx
+++ b/Luban/Config/Datas/LevelRating.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -758,14 +758,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>350</v>
+        <v>1050</v>
       </c>
       <c r="H4" t="n">
         <v>500</v>
@@ -783,16 +783,16 @@
         <v>1250</v>
       </c>
       <c r="M4" t="n">
-        <v>440000</v>
+        <v>825000</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>3138990</t>
+          <t>10016783</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>270262c0ebe4f3dde953f8a829b0a272ffe4ebbeb9ff5b04226e593ecaa30561</t>
+          <t>71cfb240594186b951d9575a98a53788d0e8c9c98d363f19694032be34b0318d</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -830,14 +830,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>370</v>
+        <v>1075</v>
       </c>
       <c r="H5" t="n">
         <v>500</v>
@@ -855,16 +855,16 @@
         <v>1250</v>
       </c>
       <c r="M5" t="n">
-        <v>455000</v>
+        <v>800000</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>3178990</t>
+          <t>10016839</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>4156e930460f120948237b05f016a0f5b64b556445f55d9ea0ff4531325b22d4</t>
+          <t>68939f5111b46bf6c26fc167c45659ca90f2c8346ee9c5dc45a03a463a621dbd</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -902,14 +902,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>390</v>
+        <v>1100</v>
       </c>
       <c r="H6" t="n">
         <v>500</v>
@@ -927,16 +927,16 @@
         <v>1250</v>
       </c>
       <c r="M6" t="n">
-        <v>470000</v>
+        <v>860000</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>3218990</t>
+          <t>10016900</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3e22a850722b74c4991980e6847ad78ba4b8e6c870a598d867fbacd2a177b328</t>
+          <t>9092ec7746dd7912687719e49cf32fa5dbdcd519d0560722e0a6a60b8f9c80f1</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -974,14 +974,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>410</v>
+        <v>1125</v>
       </c>
       <c r="H7" t="n">
         <v>500</v>
@@ -999,16 +999,16 @@
         <v>1250</v>
       </c>
       <c r="M7" t="n">
-        <v>480000</v>
+        <v>905000</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>3258990</t>
+          <t>10016971</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>ce4797bb10c34185aa56760312c52dfc6ca21044beadd6423bc08a3ac0055b7f</t>
+          <t>7af491d308eb68238a32b60e132e3008d1c2cca7f68648a634483b345db2ccfb</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1046,14 +1046,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>430</v>
+        <v>1150</v>
       </c>
       <c r="H8" t="n">
         <v>500</v>
@@ -1071,16 +1071,16 @@
         <v>1250</v>
       </c>
       <c r="M8" t="n">
-        <v>535000</v>
+        <v>870000</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3288254,3298990</t>
+          <t>3288254,3298254,10017047</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>d303daecd59ebe1630f3b3c81e810b0074cb72dce9b54fd5092537dafee3afc1</t>
+          <t>397b54d3e1fce770fb3b03909727c9fe4cd14dd3563bb5c44cfad25352d45a6f</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1118,14 +1118,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>450</v>
+        <v>1175</v>
       </c>
       <c r="H9" t="n">
         <v>500</v>
@@ -1143,16 +1143,16 @@
         <v>1250</v>
       </c>
       <c r="M9" t="n">
-        <v>545000</v>
+        <v>1055000</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>3328326,3338990</t>
+          <t>3328326,3338326,10017128</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>125cad8dede42cacbf35a9fe58e6531f1e5606549b9dcd61a45991a60182daa8</t>
+          <t>8b226230de1a341237298e0a1d83318abdb1914397d036fcff072499d6c796d1</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1190,14 +1190,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>470</v>
+        <v>1200</v>
       </c>
       <c r="H10" t="n">
         <v>500</v>
@@ -1215,16 +1215,16 @@
         <v>1250</v>
       </c>
       <c r="M10" t="n">
-        <v>560000</v>
+        <v>1010000</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3368326,3378990</t>
+          <t>3368326,3378326,10017214</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>18991c70e70e8405a0b297bd0e89e17a1a8ffbea3b7189e515db3ad987938dc7</t>
+          <t>cbc8cc3beb0cc9bd4ee77e007a81f47f8dd4d916b70d5ee582cf7fc32d6a20dc</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1262,14 +1262,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>490</v>
+        <v>1225</v>
       </c>
       <c r="H11" t="n">
         <v>500</v>
@@ -1287,16 +1287,16 @@
         <v>1250</v>
       </c>
       <c r="M11" t="n">
-        <v>570000</v>
+        <v>985000</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3409022,3418990</t>
+          <t>3409022,3419022,10017304</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>d00277d1fc0341f7580d03518a9acf76fbf0eb754e25e0b2f13782d1fa610b24</t>
+          <t>f5c3c69eeab80619bb094e92a15b1a21bea2d282597045b5129f1cd4f1a19246</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>510</v>
+        <v>1250</v>
       </c>
       <c r="H12" t="n">
         <v>500</v>
@@ -1359,16 +1359,16 @@
         <v>1250</v>
       </c>
       <c r="M12" t="n">
-        <v>625000</v>
+        <v>1035000</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3449022,3458990</t>
+          <t>3449022,3459022,10017400</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>c2e8dfbadab50017a80b400da9674a0bb4fb978daa1e9b942fa90572bb2c846b</t>
+          <t>14e5aab5c08db2dff25c5547c49ff200c91abe45560addf6f1af1ab6a0d236b0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1406,14 +1406,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>530</v>
+        <v>1275</v>
       </c>
       <c r="H13" t="n">
         <v>500</v>
@@ -1431,16 +1431,16 @@
         <v>1250</v>
       </c>
       <c r="M13" t="n">
-        <v>635000</v>
+        <v>1040000</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3488566,3498990</t>
+          <t>3488566,3498566,10017499</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0c6ab82a1bdf76517f2faa94824b3cd695925758131c0bfcf11d832790fb67b1</t>
+          <t>8d07b1b872860bd31d90bdb132d5467a2b28b2557425bbae294dea9cd49025d0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1478,14 +1478,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>550</v>
+        <v>1300</v>
       </c>
       <c r="H14" t="n">
         <v>500</v>
@@ -1503,16 +1503,16 @@
         <v>1250</v>
       </c>
       <c r="M14" t="n">
-        <v>645000</v>
+        <v>1000000</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>3528542,3538990</t>
+          <t>3528542,3538542,10017599</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>4eecd7fbe69057ad313723267aa01c8b9aab5dab5372f00471a89ff455b3292c</t>
+          <t>88c1efbee1727105b307488043ac6afdda78944ec3dec582e6c801160db0e498</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1550,14 +1550,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>570</v>
+        <v>1325</v>
       </c>
       <c r="H15" t="n">
         <v>500</v>
@@ -1575,21 +1575,21 @@
         <v>1250</v>
       </c>
       <c r="M15" t="n">
-        <v>660000</v>
+        <v>940000</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>3579039</t>
+          <t>10017701</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>3568542,3579039</t>
+          <t>3568542,3578542,10017701</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>a74842a7277464932190e0bcbf7de31e1ab0be568cce48d90dcd4057cb32513f</t>
+          <t>296710daa3cc802caa294f550117ed0e44bdb1b41cb2094d8f8b88f4cab21e39</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1627,14 +1627,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>590</v>
+        <v>1350</v>
       </c>
       <c r="H16" t="n">
         <v>500</v>
@@ -1652,21 +1652,21 @@
         <v>1250</v>
       </c>
       <c r="M16" t="n">
-        <v>710000</v>
+        <v>1050000</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3619047</t>
+          <t>10017802</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>3608542,3619047</t>
+          <t>3608542,3618542,10017802</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>b169fa0a059025afbd2f4e06cd1189b396bed6a515a0b63d74fd945d420acb8e</t>
+          <t>434b7dcf79b7ce0b434a7359661c06153ed9a84bec557a59e8361c54a29958d3</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1704,14 +1704,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>610</v>
+        <v>1375</v>
       </c>
       <c r="H17" t="n">
         <v>500</v>
@@ -1729,21 +1729,21 @@
         <v>1250</v>
       </c>
       <c r="M17" t="n">
-        <v>720000</v>
+        <v>1095000</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3659055</t>
+          <t>10017903</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>3648542,3659055</t>
+          <t>3648542,3658542,10017903</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>fad69bec09f0a6ae6b8b158b76de1fbdd814ad4f185474861069ecfeff3f66c4</t>
+          <t>03351d469611a5c205ed79b310a18b114becba0064af80a8733b83cb4450a78a</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
         <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1781,14 +1781,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G18" t="n">
-        <v>630</v>
+        <v>1400</v>
       </c>
       <c r="H18" t="n">
         <v>500</v>
@@ -1806,21 +1806,21 @@
         <v>1250</v>
       </c>
       <c r="M18" t="n">
-        <v>730000</v>
+        <v>1105000</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3699063</t>
+          <t>10018005</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>3688542,3699063</t>
+          <t>3688542,3698542,10018005</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ae05c87d52937edacf3a9e1418f97719b6537745411a5efe619456a5dfeabcbd</t>
+          <t>63a857af4df7d34857698976e11398bf900064ffc445a1c9a78b2e02fabdf42d</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1858,14 +1858,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>650</v>
+        <v>1425</v>
       </c>
       <c r="H19" t="n">
         <v>500</v>
@@ -1883,21 +1883,21 @@
         <v>1250</v>
       </c>
       <c r="M19" t="n">
-        <v>740000</v>
+        <v>1075000</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3739063</t>
+          <t>10018107</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>3728542,3739063</t>
+          <t>3728542,3738542,10018107</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>7c565be7a6eabf1645db98eccb47570e48e7973736f21b9b7cc60e8cfc72eb81</t>
+          <t>60e317a75fe77525be21fa0606236dc4b7d54ba0ce5a551a2dc5663d33b439d2</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
         <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1935,14 +1935,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>670</v>
+        <v>1450</v>
       </c>
       <c r="H20" t="n">
         <v>500</v>
@@ -1960,21 +1960,21 @@
         <v>1250</v>
       </c>
       <c r="M20" t="n">
-        <v>795000</v>
+        <v>1045000</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3779063</t>
+          <t>10018210</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>3768542,3779063</t>
+          <t>3768542,3778542,10018210</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>f24351dc13f6ffba32e6df8875818475a8aa0a4247789434111f13b58c9925f9</t>
+          <t>f75eb61bf5823e5fce625900b13cc91e4c23d01de38bf7c3fac185b6634bef43</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
         <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2012,14 +2012,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>690</v>
+        <v>1475</v>
       </c>
       <c r="H21" t="n">
         <v>500</v>
@@ -2037,21 +2037,21 @@
         <v>1250</v>
       </c>
       <c r="M21" t="n">
-        <v>805000</v>
+        <v>1080000</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3819063</t>
+          <t>10018313</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>3808542,3819063</t>
+          <t>3808542,3818542,10018313</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>98c126a8504574c893c150c550efe7a5633598eb25d3c812452983fcfb154055</t>
+          <t>ef560680f9a0a8f55ecc28bc146521ea26c804f54714c59a9781008ee8e169ad</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
         <v>19</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2089,14 +2089,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>710</v>
+        <v>1500</v>
       </c>
       <c r="H22" t="n">
         <v>500</v>
@@ -2114,21 +2114,21 @@
         <v>1250</v>
       </c>
       <c r="M22" t="n">
-        <v>815000</v>
+        <v>1145000</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3859063</t>
+          <t>10018417</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>3848542,3859063</t>
+          <t>3848542,3858542,10018417</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>fe0fd45eea6ce92077ae07f9f8b077458d8d99f23ba27466b866a838645e872f</t>
+          <t>cb1a11696bfea4ffc1dd756b0fe4bd5fd569a1b3f16cc298853b66982728467d</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         <v>20</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2166,14 +2166,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>730</v>
+        <v>1525</v>
       </c>
       <c r="H23" t="n">
         <v>500</v>
@@ -2191,21 +2191,21 @@
         <v>1250</v>
       </c>
       <c r="M23" t="n">
-        <v>825000</v>
+        <v>1100000</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3899063</t>
+          <t>10018521</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3888542,3899063</t>
+          <t>3888542,3898542,10018521</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>balance-20x20-v1</t>
+          <t>balance-30x25-maze-v3</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>7a6ff581cd39795f167a137a80fa3196385d7ea18e07657805cfc7da4d0ae64c</t>
+          <t>0c675a9ce5dc120e6bd33000d1c651c4daa1808b622d531009823e080026d486</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2225,7 +2225,777 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>f7d9caf8af2ee6de5f8b58bece6af8b829b7efaa265eb3442f0fed9f5b2b87ea</t>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H24" t="n">
+        <v>500</v>
+      </c>
+      <c r="I24" t="n">
+        <v>750</v>
+      </c>
+      <c r="J24" t="n">
+        <v>900</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>10018896</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>10018684,10018781,10018896</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>balance-30x25-maze-v3</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>five-stars-v1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>ea647c48e1b0651e410f9119c7194642658f5612b975beefa184a4d371863056</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>verified_unity_reference</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1575</v>
+      </c>
+      <c r="H25" t="n">
+        <v>500</v>
+      </c>
+      <c r="I25" t="n">
+        <v>750</v>
+      </c>
+      <c r="J25" t="n">
+        <v>900</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>10019271</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>10019058,10019156,10019271</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>balance-30x25-maze-v3</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>five-stars-v1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>b12a871f1b79ee4a6617392b549a42e922236864ae301624f5f584af70f48307</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>verified_unity_reference</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>25</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H26" t="n">
+        <v>500</v>
+      </c>
+      <c r="I26" t="n">
+        <v>750</v>
+      </c>
+      <c r="J26" t="n">
+        <v>900</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>10019649</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>10019435,10019533,10019649</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>balance-30x25-maze-v3</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>five-stars-v1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>6e253ef51fa7a5e89a0264d25f7796f048dc9d9b4bb5d24c92063a588dc15a13</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>verified_unity_reference</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1625</v>
+      </c>
+      <c r="H27" t="n">
+        <v>500</v>
+      </c>
+      <c r="I27" t="n">
+        <v>750</v>
+      </c>
+      <c r="J27" t="n">
+        <v>900</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>10020027</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>10019814,10019910,10020027</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>balance-30x25-maze-v3</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>five-stars-v1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>59746fa126bb8c263debf2d606f165c08a5d84e9fc0d25b1e4a4adcf9961aa0d</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>verified_unity_reference</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1650</v>
+      </c>
+      <c r="H28" t="n">
+        <v>500</v>
+      </c>
+      <c r="I28" t="n">
+        <v>750</v>
+      </c>
+      <c r="J28" t="n">
+        <v>900</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1265000</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>10020407</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>10020192,10020290,10020407</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>balance-30x25-maze-v3</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>five-stars-v1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>8261d4fb66cd05674bd376242184594da3ebf3a5f0b1832d75c6f61420b3e2f2</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>verified_unity_reference</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>25</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1675</v>
+      </c>
+      <c r="H29" t="n">
+        <v>500</v>
+      </c>
+      <c r="I29" t="n">
+        <v>750</v>
+      </c>
+      <c r="J29" t="n">
+        <v>900</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1145000</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>10020787</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>10020572,10020670,10020787</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>balance-30x25-maze-v3</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>five-stars-v1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>53d4580491569c01da7231510f2a363604b83bfa5626b0c81683ec29eed53262</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>verified_unity_reference</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>25</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1700</v>
+      </c>
+      <c r="H30" t="n">
+        <v>500</v>
+      </c>
+      <c r="I30" t="n">
+        <v>750</v>
+      </c>
+      <c r="J30" t="n">
+        <v>900</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1305000</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>10021169</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>10020953,10021052,10021169</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>balance-30x25-maze-v3</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>five-stars-v1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>ac0976c466e0468476646c0c040fc39aea8e925e4c060a01b9ff935fd5d6806e</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>verified_unity_reference</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>25</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1725</v>
+      </c>
+      <c r="H31" t="n">
+        <v>500</v>
+      </c>
+      <c r="I31" t="n">
+        <v>750</v>
+      </c>
+      <c r="J31" t="n">
+        <v>900</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1370000</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>10021551</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>10021335,10021434,10021551</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>balance-30x25-maze-v3</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>five-stars-v1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>6623107cce4b851ef1637dd53dcc0fc22ad0f01569aaa4833f0a2b253a8baa33</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>verified_unity_reference</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>25</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1750</v>
+      </c>
+      <c r="H32" t="n">
+        <v>500</v>
+      </c>
+      <c r="I32" t="n">
+        <v>750</v>
+      </c>
+      <c r="J32" t="n">
+        <v>900</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>10021935</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>10021717,10021818,10021935</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>balance-30x25-maze-v3</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>five-stars-v1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>5d730736393ac3f1e1fd0be0f47fbe0b4467ed3c7da1a6a15ea9cfaef1390f73</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>verified_unity_reference</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>25</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1775</v>
+      </c>
+      <c r="H33" t="n">
+        <v>500</v>
+      </c>
+      <c r="I33" t="n">
+        <v>750</v>
+      </c>
+      <c r="J33" t="n">
+        <v>900</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1215000</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>10022319</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>10022101,10022202,10022319</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>balance-30x25-maze-v3</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>five-stars-v1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>5bb2b1d681acba6f9a7dca608c85c9142120975e39eb8755b4cbb81927a96c56</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>verified_unity_reference</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/LevelRating.xlsx
+++ b/Luban/Config/Datas/LevelRating.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -765,7 +765,7 @@
         <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>1050</v>
+        <v>1175</v>
       </c>
       <c r="H4" t="n">
         <v>500</v>
@@ -783,7 +783,7 @@
         <v>1250</v>
       </c>
       <c r="M4" t="n">
-        <v>825000</v>
+        <v>562000</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>71cfb240594186b951d9575a98a53788d0e8c9c98d363f19694032be34b0318d</t>
+          <t>1075be682e5c93134cb59ee26b346d860a13a5f6f700d97ed63ff24973ade8a4</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>1075</v>
+        <v>1225</v>
       </c>
       <c r="H5" t="n">
         <v>500</v>
@@ -855,7 +855,7 @@
         <v>1250</v>
       </c>
       <c r="M5" t="n">
-        <v>800000</v>
+        <v>810000</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>68939f5111b46bf6c26fc167c45659ca90f2c8346ee9c5dc45a03a463a621dbd</t>
+          <t>962934748cb2aabfef8d8f18694424a9537d7bc5c6faebfe214288c9e1e17424</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>1100</v>
+        <v>1275</v>
       </c>
       <c r="H6" t="n">
         <v>500</v>
@@ -927,7 +927,7 @@
         <v>1250</v>
       </c>
       <c r="M6" t="n">
-        <v>860000</v>
+        <v>903000</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9092ec7746dd7912687719e49cf32fa5dbdcd519d0560722e0a6a60b8f9c80f1</t>
+          <t>ba96c45500aed38e047ed6474baaeb543256799b436f114e4a3d83972b2dfad3</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>1125</v>
+        <v>1325</v>
       </c>
       <c r="H7" t="n">
         <v>500</v>
@@ -999,7 +999,7 @@
         <v>1250</v>
       </c>
       <c r="M7" t="n">
-        <v>905000</v>
+        <v>959000</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>7af491d308eb68238a32b60e132e3008d1c2cca7f68648a634483b345db2ccfb</t>
+          <t>f07243e4eafa98d9dc5265fb7211afae5f1fd5e7a383d04110c6cbfc9e1695ba</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
         <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>1150</v>
+        <v>1375</v>
       </c>
       <c r="H8" t="n">
         <v>500</v>
@@ -1071,7 +1071,7 @@
         <v>1250</v>
       </c>
       <c r="M8" t="n">
-        <v>870000</v>
+        <v>984000</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1090,17 +1090,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>397b54d3e1fce770fb3b03909727c9fe4cd14dd3563bb5c44cfad25352d45a6f</t>
+          <t>12458bd54fb4f0acd53412d8f74286daa97e9ff5e2c42ba6266557edadc0bf43</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
         <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>1175</v>
+        <v>1425</v>
       </c>
       <c r="H9" t="n">
         <v>500</v>
@@ -1143,7 +1143,7 @@
         <v>1250</v>
       </c>
       <c r="M9" t="n">
-        <v>1055000</v>
+        <v>865000</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>8b226230de1a341237298e0a1d83318abdb1914397d036fcff072499d6c796d1</t>
+          <t>dfdb6427dd37a8d270932bb803bfc8c666bb84fb968b3e44363431a2b21620b1</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
         <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>1200</v>
+        <v>1475</v>
       </c>
       <c r="H10" t="n">
         <v>500</v>
@@ -1215,7 +1215,7 @@
         <v>1250</v>
       </c>
       <c r="M10" t="n">
-        <v>1010000</v>
+        <v>1015000</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1234,17 +1234,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>cbc8cc3beb0cc9bd4ee77e007a81f47f8dd4d916b70d5ee582cf7fc32d6a20dc</t>
+          <t>bfdadfdcaf9870e9fee0e109372543f437acbfdb09d19a379e41de94b33b614c</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>1225</v>
+        <v>1525</v>
       </c>
       <c r="H11" t="n">
         <v>500</v>
@@ -1287,7 +1287,7 @@
         <v>1250</v>
       </c>
       <c r="M11" t="n">
-        <v>985000</v>
+        <v>1003000</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1306,17 +1306,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>f5c3c69eeab80619bb094e92a15b1a21bea2d282597045b5129f1cd4f1a19246</t>
+          <t>6542980de51447ab397fb236965415aa43cd5202e0886db1b3612997d60aa029</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>1250</v>
+        <v>1575</v>
       </c>
       <c r="H12" t="n">
         <v>500</v>
@@ -1359,7 +1359,7 @@
         <v>1250</v>
       </c>
       <c r="M12" t="n">
-        <v>1035000</v>
+        <v>1034000</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>14e5aab5c08db2dff25c5547c49ff200c91abe45560addf6f1af1ab6a0d236b0</t>
+          <t>431ddda5fc1963e79f44973601f469cbaa7e5731f4db986cd1804382f3bdda6f</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>1275</v>
+        <v>1625</v>
       </c>
       <c r="H13" t="n">
         <v>500</v>
@@ -1431,7 +1431,7 @@
         <v>1250</v>
       </c>
       <c r="M13" t="n">
-        <v>1040000</v>
+        <v>1085000</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>8d07b1b872860bd31d90bdb132d5467a2b28b2557425bbae294dea9cd49025d0</t>
+          <t>4bfabd2a5707b515884228683f3188c765c833c300a4f826a88cdea31ff36678</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>1300</v>
+        <v>1675</v>
       </c>
       <c r="H14" t="n">
         <v>500</v>
@@ -1503,7 +1503,7 @@
         <v>1250</v>
       </c>
       <c r="M14" t="n">
-        <v>1000000</v>
+        <v>1077000</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1522,17 +1522,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>88c1efbee1727105b307488043ac6afdda78944ec3dec582e6c801160db0e498</t>
+          <t>899737570d9d53effe6a1faad11928b624d437b4cef894326b7e6a734a42406c</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>1325</v>
+        <v>1725</v>
       </c>
       <c r="H15" t="n">
         <v>500</v>
@@ -1575,7 +1575,7 @@
         <v>1250</v>
       </c>
       <c r="M15" t="n">
-        <v>940000</v>
+        <v>1104000</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1599,17 +1599,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>296710daa3cc802caa294f550117ed0e44bdb1b41cb2094d8f8b88f4cab21e39</t>
+          <t>61564ce6e1a54ceb91dd5560cfda753fe81e3231a96e2011f19b98c799c14559</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>1350</v>
+        <v>1775</v>
       </c>
       <c r="H16" t="n">
         <v>500</v>
@@ -1652,7 +1652,7 @@
         <v>1250</v>
       </c>
       <c r="M16" t="n">
-        <v>1050000</v>
+        <v>958000</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>434b7dcf79b7ce0b434a7359661c06153ed9a84bec557a59e8361c54a29958d3</t>
+          <t>095ff11b4e3730f55281c53a7624798244453945460e69deddd37087c17a1a4f</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
         <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>1375</v>
+        <v>1825</v>
       </c>
       <c r="H17" t="n">
         <v>500</v>
@@ -1729,7 +1729,7 @@
         <v>1250</v>
       </c>
       <c r="M17" t="n">
-        <v>1095000</v>
+        <v>1074000</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1753,17 +1753,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03351d469611a5c205ed79b310a18b114becba0064af80a8733b83cb4450a78a</t>
+          <t>6c267524f294e6af02c8eb50dadd414ad5233b57ab836152febbc9c6cf050a36</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="G18" t="n">
-        <v>1400</v>
+        <v>1875</v>
       </c>
       <c r="H18" t="n">
         <v>500</v>
@@ -1806,7 +1806,7 @@
         <v>1250</v>
       </c>
       <c r="M18" t="n">
-        <v>1105000</v>
+        <v>1106000</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1830,17 +1830,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>63a857af4df7d34857698976e11398bf900064ffc445a1c9a78b2e02fabdf42d</t>
+          <t>3ab76b0996d15a540b5219b18f50de484a038597eaa3aacf63fbf525454dd83b</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
         <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>1425</v>
+        <v>1925</v>
       </c>
       <c r="H19" t="n">
         <v>500</v>
@@ -1883,7 +1883,7 @@
         <v>1250</v>
       </c>
       <c r="M19" t="n">
-        <v>1075000</v>
+        <v>1111000</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>60e317a75fe77525be21fa0606236dc4b7d54ba0ce5a551a2dc5663d33b439d2</t>
+          <t>f1e063e82fb0e1b4b4ffb2356f857987b9cfb41469f663841f0a54841b02b31f</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>1450</v>
+        <v>1975</v>
       </c>
       <c r="H20" t="n">
         <v>500</v>
@@ -1960,7 +1960,7 @@
         <v>1250</v>
       </c>
       <c r="M20" t="n">
-        <v>1045000</v>
+        <v>1103000</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1984,17 +1984,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>f75eb61bf5823e5fce625900b13cc91e4c23d01de38bf7c3fac185b6634bef43</t>
+          <t>0a1ffc21ae8273f1b556c3792924f3e72104f2e342a751f7a14cd17a8f5492de</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
         <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>1475</v>
+        <v>2025</v>
       </c>
       <c r="H21" t="n">
         <v>500</v>
@@ -2037,7 +2037,7 @@
         <v>1250</v>
       </c>
       <c r="M21" t="n">
-        <v>1080000</v>
+        <v>1074000</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ef560680f9a0a8f55ecc28bc146521ea26c804f54714c59a9781008ee8e169ad</t>
+          <t>f4b316e6ef3c8c2c1a4b67cc71d3ae72cc06cf93278eb62a375e2be77193ab12</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
         <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>1500</v>
+        <v>2075</v>
       </c>
       <c r="H22" t="n">
         <v>500</v>
@@ -2114,7 +2114,7 @@
         <v>1250</v>
       </c>
       <c r="M22" t="n">
-        <v>1145000</v>
+        <v>1161000</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2138,17 +2138,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>cb1a11696bfea4ffc1dd756b0fe4bd5fd569a1b3f16cc298853b66982728467d</t>
+          <t>16b97693500a5a731a914e1046b3886bd7bf54496df54c5df2d4acea7dd6e254</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>1525</v>
+        <v>2125</v>
       </c>
       <c r="H23" t="n">
         <v>500</v>
@@ -2191,7 +2191,7 @@
         <v>1250</v>
       </c>
       <c r="M23" t="n">
-        <v>1100000</v>
+        <v>1145000</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2215,17 +2215,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0c675a9ce5dc120e6bd33000d1c651c4daa1808b622d531009823e080026d486</t>
+          <t>ad522e8e1964812eda8e844113df6375674ca4fa58cf862e3da7feba914f8ecf</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
         <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>1550</v>
+        <v>2175</v>
       </c>
       <c r="H24" t="n">
         <v>500</v>
@@ -2268,7 +2268,7 @@
         <v>1250</v>
       </c>
       <c r="M24" t="n">
-        <v>1165000</v>
+        <v>1149000</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2292,17 +2292,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ea647c48e1b0651e410f9119c7194642658f5612b975beefa184a4d371863056</t>
+          <t>e890a43b71003f1afc79caaae56e3dc4052ddd957a75824605c2662b538ce9c3</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>1575</v>
+        <v>2225</v>
       </c>
       <c r="H25" t="n">
         <v>500</v>
@@ -2345,7 +2345,7 @@
         <v>1250</v>
       </c>
       <c r="M25" t="n">
-        <v>1150000</v>
+        <v>1040000</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2369,17 +2369,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>b12a871f1b79ee4a6617392b549a42e922236864ae301624f5f584af70f48307</t>
+          <t>5a4db93ba5f1e3930c4ef729f6157d55772414ed7e96ffe8f8d3ffeb4c52e7be</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
         <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>1600</v>
+        <v>2275</v>
       </c>
       <c r="H26" t="n">
         <v>500</v>
@@ -2422,7 +2422,7 @@
         <v>1250</v>
       </c>
       <c r="M26" t="n">
-        <v>1225000</v>
+        <v>1109000</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>6e253ef51fa7a5e89a0264d25f7796f048dc9d9b4bb5d24c92063a588dc15a13</t>
+          <t>ae0f4a6647a84465ca69a74a624a75fc44fa1ccae507affcf14d0c895cf8fd67</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>1625</v>
+        <v>2325</v>
       </c>
       <c r="H27" t="n">
         <v>500</v>
@@ -2499,7 +2499,7 @@
         <v>1250</v>
       </c>
       <c r="M27" t="n">
-        <v>1175000</v>
+        <v>1138000</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2523,17 +2523,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>59746fa126bb8c263debf2d606f165c08a5d84e9fc0d25b1e4a4adcf9961aa0d</t>
+          <t>109149429abff5cd0e1587348dd309368099b30d7c313523122a73a09d9cd83e</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
         <v>25</v>
       </c>
       <c r="G28" t="n">
-        <v>1650</v>
+        <v>2375</v>
       </c>
       <c r="H28" t="n">
         <v>500</v>
@@ -2576,7 +2576,7 @@
         <v>1250</v>
       </c>
       <c r="M28" t="n">
-        <v>1265000</v>
+        <v>1180000</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2600,17 +2600,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>8261d4fb66cd05674bd376242184594da3ebf3a5f0b1832d75c6f61420b3e2f2</t>
+          <t>04e3f0e5358e7bd7af1824cad7a9429146c68c35539bac245293aab85a979516</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>1675</v>
+        <v>2425</v>
       </c>
       <c r="H29" t="n">
         <v>500</v>
@@ -2653,7 +2653,7 @@
         <v>1250</v>
       </c>
       <c r="M29" t="n">
-        <v>1145000</v>
+        <v>1081000</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2677,17 +2677,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>53d4580491569c01da7231510f2a363604b83bfa5626b0c81683ec29eed53262</t>
+          <t>f0f9a727a4d660555a9f7c3d0d3eef5354b45dcf0441fbb44418c30db146f31a</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>1700</v>
+        <v>2475</v>
       </c>
       <c r="H30" t="n">
         <v>500</v>
@@ -2730,7 +2730,7 @@
         <v>1250</v>
       </c>
       <c r="M30" t="n">
-        <v>1305000</v>
+        <v>1166000</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2754,17 +2754,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>ac0976c466e0468476646c0c040fc39aea8e925e4c060a01b9ff935fd5d6806e</t>
+          <t>19b0acb0bcf7ab1316685ca441f9302cdb7e536d55bfb7c538139d4cea48fbfc</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
         <v>25</v>
       </c>
       <c r="G31" t="n">
-        <v>1725</v>
+        <v>2525</v>
       </c>
       <c r="H31" t="n">
         <v>500</v>
@@ -2807,7 +2807,7 @@
         <v>1250</v>
       </c>
       <c r="M31" t="n">
-        <v>1370000</v>
+        <v>1093000</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6623107cce4b851ef1637dd53dcc0fc22ad0f01569aaa4833f0a2b253a8baa33</t>
+          <t>3b5af52878c1972d2d7f6d4335af33e15b8ce31022a0d776c61718468db3896c</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
         <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>1750</v>
+        <v>2575</v>
       </c>
       <c r="H32" t="n">
         <v>500</v>
@@ -2884,7 +2884,7 @@
         <v>1250</v>
       </c>
       <c r="M32" t="n">
-        <v>1360000</v>
+        <v>1210000</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2908,17 +2908,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>5d730736393ac3f1e1fd0be0f47fbe0b4467ed3c7da1a6a15ea9cfaef1390f73</t>
+          <t>7f570c10217cd4c44d3771291a42b6c4c200515ed89512222ae77aee638dcbb9</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
         <v>25</v>
       </c>
       <c r="G33" t="n">
-        <v>1775</v>
+        <v>2625</v>
       </c>
       <c r="H33" t="n">
         <v>500</v>
@@ -2961,7 +2961,7 @@
         <v>1250</v>
       </c>
       <c r="M33" t="n">
-        <v>1215000</v>
+        <v>1225000</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>balance-30x25-maze-v3</t>
+          <t>balance-30x25-tight-v5</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2985,17 +2985,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>5bb2b1d681acba6f9a7dca608c85c9142120975e39eb8755b4cbb81927a96c56</t>
+          <t>4c7fb983c5d08f426c355de4a1f649169126cbfbac44f2a2fe4934d210ccff1d</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>verified_unity_reference</t>
+          <t>pending_unity_reference</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>d5870ef4b2972e44ccc3fc735dfc3c377932d849ac41982509f08c4866d7e8b3</t>
+          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/LevelRating.xlsx
+++ b/Luban/Config/Datas/LevelRating.xlsx
@@ -765,7 +765,7 @@
         <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>1175</v>
+        <v>2250</v>
       </c>
       <c r="H4" t="n">
         <v>500</v>
@@ -783,7 +783,7 @@
         <v>1250</v>
       </c>
       <c r="M4" t="n">
-        <v>562000</v>
+        <v>945000</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1075be682e5c93134cb59ee26b346d860a13a5f6f700d97ed63ff24973ade8a4</t>
+          <t>e16724cb2fad7ecda23c38badfee3bc49bb2df8f87ca9148c865d688a5221bc5</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>1225</v>
+        <v>2300</v>
       </c>
       <c r="H5" t="n">
         <v>500</v>
@@ -855,7 +855,7 @@
         <v>1250</v>
       </c>
       <c r="M5" t="n">
-        <v>810000</v>
+        <v>960000</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>962934748cb2aabfef8d8f18694424a9537d7bc5c6faebfe214288c9e1e17424</t>
+          <t>664ace75ff6b76ce35ed6f8e5d352032831ebed94dec39a287561cadc506ba5b</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>1275</v>
+        <v>2350</v>
       </c>
       <c r="H6" t="n">
         <v>500</v>
@@ -927,7 +927,7 @@
         <v>1250</v>
       </c>
       <c r="M6" t="n">
-        <v>903000</v>
+        <v>970000</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ba96c45500aed38e047ed6474baaeb543256799b436f114e4a3d83972b2dfad3</t>
+          <t>c8aa593e12c35eb894a3041c06abab10bc1568964e398415dea59356b39905a4</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>1325</v>
+        <v>2400</v>
       </c>
       <c r="H7" t="n">
         <v>500</v>
@@ -999,7 +999,7 @@
         <v>1250</v>
       </c>
       <c r="M7" t="n">
-        <v>959000</v>
+        <v>980000</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>f07243e4eafa98d9dc5265fb7211afae5f1fd5e7a383d04110c6cbfc9e1695ba</t>
+          <t>14e52117f945194786731e04f333770a010aff85e77177a02103cc286b555295</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
         <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>1375</v>
+        <v>2450</v>
       </c>
       <c r="H8" t="n">
         <v>500</v>
@@ -1071,7 +1071,7 @@
         <v>1250</v>
       </c>
       <c r="M8" t="n">
-        <v>984000</v>
+        <v>995000</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>12458bd54fb4f0acd53412d8f74286daa97e9ff5e2c42ba6266557edadc0bf43</t>
+          <t>c62ab6630d4ec7d9d1e40deaa9c321f32906076b084a8568d55e51db2934c2e1</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
         <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>1425</v>
+        <v>2500</v>
       </c>
       <c r="H9" t="n">
         <v>500</v>
@@ -1143,7 +1143,7 @@
         <v>1250</v>
       </c>
       <c r="M9" t="n">
-        <v>865000</v>
+        <v>1005000</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>dfdb6427dd37a8d270932bb803bfc8c666bb84fb968b3e44363431a2b21620b1</t>
+          <t>b4fe7fdb97e8c53ff71f0a758051b0cce0606db1907f4abc651c73f6f1b5e053</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
         <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>1475</v>
+        <v>2550</v>
       </c>
       <c r="H10" t="n">
         <v>500</v>
@@ -1215,7 +1215,7 @@
         <v>1250</v>
       </c>
       <c r="M10" t="n">
-        <v>1015000</v>
+        <v>1055000</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>bfdadfdcaf9870e9fee0e109372543f437acbfdb09d19a379e41de94b33b614c</t>
+          <t>7dac1163e432cb97caf6121f069e1a5121940d59d39b172ab5cf18d986eaacf9</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>1525</v>
+        <v>2600</v>
       </c>
       <c r="H11" t="n">
         <v>500</v>
@@ -1287,7 +1287,7 @@
         <v>1250</v>
       </c>
       <c r="M11" t="n">
-        <v>1003000</v>
+        <v>1065000</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>6542980de51447ab397fb236965415aa43cd5202e0886db1b3612997d60aa029</t>
+          <t>78c474366defbcd58ebffa03d8f5bc5e4d5c59fa702c151e2ac6020ca3a301a3</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>1575</v>
+        <v>2650</v>
       </c>
       <c r="H12" t="n">
         <v>500</v>
@@ -1359,7 +1359,7 @@
         <v>1250</v>
       </c>
       <c r="M12" t="n">
-        <v>1034000</v>
+        <v>1075000</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>431ddda5fc1963e79f44973601f469cbaa7e5731f4db986cd1804382f3bdda6f</t>
+          <t>0b8053f6142bffbd1f473e3804e244d957d9388149b20f4840f7b8b01ba8f627</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>1625</v>
+        <v>2700</v>
       </c>
       <c r="H13" t="n">
         <v>500</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>4bfabd2a5707b515884228683f3188c765c833c300a4f826a88cdea31ff36678</t>
+          <t>1811ae4771ef36bd2f2f2628cabc4b60196488b4b7dbd3bb685f5e20b1e4b062</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>1675</v>
+        <v>2750</v>
       </c>
       <c r="H14" t="n">
         <v>500</v>
@@ -1503,7 +1503,7 @@
         <v>1250</v>
       </c>
       <c r="M14" t="n">
-        <v>1077000</v>
+        <v>1095000</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>899737570d9d53effe6a1faad11928b624d437b4cef894326b7e6a734a42406c</t>
+          <t>2e9f9014cb187b40444609c7bc34609a1c4d8220fdfcd8ae40dff9834963f704</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>1725</v>
+        <v>2800</v>
       </c>
       <c r="H15" t="n">
         <v>500</v>
@@ -1575,7 +1575,7 @@
         <v>1250</v>
       </c>
       <c r="M15" t="n">
-        <v>1104000</v>
+        <v>1105000</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>61564ce6e1a54ceb91dd5560cfda753fe81e3231a96e2011f19b98c799c14559</t>
+          <t>bb8c5e06744154d924d2e488c3e1e7ad425d923da8e3d57f1a3250d97f19f0b5</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>1775</v>
+        <v>2850</v>
       </c>
       <c r="H16" t="n">
         <v>500</v>
@@ -1652,7 +1652,7 @@
         <v>1250</v>
       </c>
       <c r="M16" t="n">
-        <v>958000</v>
+        <v>1155000</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>095ff11b4e3730f55281c53a7624798244453945460e69deddd37087c17a1a4f</t>
+          <t>f7637af7544a562687a9de4574a2d4239ff0f60be721d925bbe656024c2f28f9</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
         <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>1825</v>
+        <v>2900</v>
       </c>
       <c r="H17" t="n">
         <v>500</v>
@@ -1729,7 +1729,7 @@
         <v>1250</v>
       </c>
       <c r="M17" t="n">
-        <v>1074000</v>
+        <v>1165000</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>6c267524f294e6af02c8eb50dadd414ad5233b57ab836152febbc9c6cf050a36</t>
+          <t>c28b9c762aa94dfc407e04649bc1dbfba54a76617d7d2596c2f49fb4ab15fe98</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="G18" t="n">
-        <v>1875</v>
+        <v>2950</v>
       </c>
       <c r="H18" t="n">
         <v>500</v>
@@ -1806,7 +1806,7 @@
         <v>1250</v>
       </c>
       <c r="M18" t="n">
-        <v>1106000</v>
+        <v>1175000</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>3ab76b0996d15a540b5219b18f50de484a038597eaa3aacf63fbf525454dd83b</t>
+          <t>4f2b47f115c58bfff56efeb1184129a0d2d82d125cfdcf0d1c7c2948c16b54a4</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
         <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>1925</v>
+        <v>3000</v>
       </c>
       <c r="H19" t="n">
         <v>500</v>
@@ -1883,7 +1883,7 @@
         <v>1250</v>
       </c>
       <c r="M19" t="n">
-        <v>1111000</v>
+        <v>1185000</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>f1e063e82fb0e1b4b4ffb2356f857987b9cfb41469f663841f0a54841b02b31f</t>
+          <t>2c9eb8013b256405953ed1d9b7102f9dd7bb31809267fcc2b13ead7f81b099e6</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>1975</v>
+        <v>3050</v>
       </c>
       <c r="H20" t="n">
         <v>500</v>
@@ -1960,7 +1960,7 @@
         <v>1250</v>
       </c>
       <c r="M20" t="n">
-        <v>1103000</v>
+        <v>1195000</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0a1ffc21ae8273f1b556c3792924f3e72104f2e342a751f7a14cd17a8f5492de</t>
+          <t>03847a3318de28f8adadb7ff4f1e46638b683ff983e010d5820105439d58c860</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
         <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>2025</v>
+        <v>3100</v>
       </c>
       <c r="H21" t="n">
         <v>500</v>
@@ -2037,7 +2037,7 @@
         <v>1250</v>
       </c>
       <c r="M21" t="n">
-        <v>1074000</v>
+        <v>1205000</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>f4b316e6ef3c8c2c1a4b67cc71d3ae72cc06cf93278eb62a375e2be77193ab12</t>
+          <t>0904ff44fbecab8745fbc8bad5338473da9eb8f27197d1c91843fa84a51c3aaa</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
         <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>2075</v>
+        <v>3150</v>
       </c>
       <c r="H22" t="n">
         <v>500</v>
@@ -2114,7 +2114,7 @@
         <v>1250</v>
       </c>
       <c r="M22" t="n">
-        <v>1161000</v>
+        <v>1255000</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>16b97693500a5a731a914e1046b3886bd7bf54496df54c5df2d4acea7dd6e254</t>
+          <t>798c59157c9d4122955c6a018b9cb12af089210cea473c9f27df967eca7f7e95</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>2125</v>
+        <v>3200</v>
       </c>
       <c r="H23" t="n">
         <v>500</v>
@@ -2191,7 +2191,7 @@
         <v>1250</v>
       </c>
       <c r="M23" t="n">
-        <v>1145000</v>
+        <v>1260000</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ad522e8e1964812eda8e844113df6375674ca4fa58cf862e3da7feba914f8ecf</t>
+          <t>7b70e3d7dfaa36a4f54fb9167c423580d2ab0176c8bf67db97aa9cff1321203e</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
         <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>2175</v>
+        <v>3250</v>
       </c>
       <c r="H24" t="n">
         <v>500</v>
@@ -2268,7 +2268,7 @@
         <v>1250</v>
       </c>
       <c r="M24" t="n">
-        <v>1149000</v>
+        <v>1270000</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>e890a43b71003f1afc79caaae56e3dc4052ddd957a75824605c2662b538ce9c3</t>
+          <t>6d2ad822a1b06d3fa411595902cdb981d20ec08a285d0cc83b0bbe078b79a316</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>2225</v>
+        <v>3300</v>
       </c>
       <c r="H25" t="n">
         <v>500</v>
@@ -2345,7 +2345,7 @@
         <v>1250</v>
       </c>
       <c r="M25" t="n">
-        <v>1040000</v>
+        <v>1280000</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>5a4db93ba5f1e3930c4ef729f6157d55772414ed7e96ffe8f8d3ffeb4c52e7be</t>
+          <t>434dcd523f968ebc0e14e2bfe0f9ac299739bdd859d2373b0297d0dbbf4f2734</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
         <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>2275</v>
+        <v>3350</v>
       </c>
       <c r="H26" t="n">
         <v>500</v>
@@ -2422,7 +2422,7 @@
         <v>1250</v>
       </c>
       <c r="M26" t="n">
-        <v>1109000</v>
+        <v>1290000</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ae0f4a6647a84465ca69a74a624a75fc44fa1ccae507affcf14d0c895cf8fd67</t>
+          <t>a27fa228f9abf0864ea76281ff8b7b48638fec4d89de6dcb69e1edbe36bd3f6b</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>2325</v>
+        <v>3400</v>
       </c>
       <c r="H27" t="n">
         <v>500</v>
@@ -2499,7 +2499,7 @@
         <v>1250</v>
       </c>
       <c r="M27" t="n">
-        <v>1138000</v>
+        <v>1300000</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>109149429abff5cd0e1587348dd309368099b30d7c313523122a73a09d9cd83e</t>
+          <t>8ea484af8a6b7e5ec91c42ba24e62e7cc486d2aeb7c6763c99e8de1353816a74</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
         <v>25</v>
       </c>
       <c r="G28" t="n">
-        <v>2375</v>
+        <v>3450</v>
       </c>
       <c r="H28" t="n">
         <v>500</v>
@@ -2576,7 +2576,7 @@
         <v>1250</v>
       </c>
       <c r="M28" t="n">
-        <v>1180000</v>
+        <v>1345000</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>04e3f0e5358e7bd7af1824cad7a9429146c68c35539bac245293aab85a979516</t>
+          <t>ddd8a6a81b14dfcce06bbc37e72c496fef5323b3e0d3d7d8f5edc8614bc46bf1</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>2425</v>
+        <v>3500</v>
       </c>
       <c r="H29" t="n">
         <v>500</v>
@@ -2653,7 +2653,7 @@
         <v>1250</v>
       </c>
       <c r="M29" t="n">
-        <v>1081000</v>
+        <v>1355000</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>f0f9a727a4d660555a9f7c3d0d3eef5354b45dcf0441fbb44418c30db146f31a</t>
+          <t>4d52c6ec51f27e3953920da8d9373b3e860411c5a41c05d651ba34a4cf0fbfae</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>2475</v>
+        <v>3550</v>
       </c>
       <c r="H30" t="n">
         <v>500</v>
@@ -2730,7 +2730,7 @@
         <v>1250</v>
       </c>
       <c r="M30" t="n">
-        <v>1166000</v>
+        <v>1365000</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>19b0acb0bcf7ab1316685ca441f9302cdb7e536d55bfb7c538139d4cea48fbfc</t>
+          <t>a7a3177cf14ebbfa531cae46e3f153267211d238b82ac9e2607994fb28786646</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
         <v>25</v>
       </c>
       <c r="G31" t="n">
-        <v>2525</v>
+        <v>3600</v>
       </c>
       <c r="H31" t="n">
         <v>500</v>
@@ -2807,7 +2807,7 @@
         <v>1250</v>
       </c>
       <c r="M31" t="n">
-        <v>1093000</v>
+        <v>1375000</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>3b5af52878c1972d2d7f6d4335af33e15b8ce31022a0d776c61718468db3896c</t>
+          <t>6a1dce400d0dc7754af352e4675c633f18bad398ed7f08aba35ded872aa30610</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
         <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>2575</v>
+        <v>3650</v>
       </c>
       <c r="H32" t="n">
         <v>500</v>
@@ -2884,7 +2884,7 @@
         <v>1250</v>
       </c>
       <c r="M32" t="n">
-        <v>1210000</v>
+        <v>1380000</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>7f570c10217cd4c44d3771291a42b6c4c200515ed89512222ae77aee638dcbb9</t>
+          <t>3951af01a1375749a332f40cc36344bb88e3340049036fc3983d80bb0318ea48</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
         <v>25</v>
       </c>
       <c r="G33" t="n">
-        <v>2625</v>
+        <v>3700</v>
       </c>
       <c r="H33" t="n">
         <v>500</v>
@@ -2961,7 +2961,7 @@
         <v>1250</v>
       </c>
       <c r="M33" t="n">
-        <v>1225000</v>
+        <v>1390000</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>balance-30x25-tight-v5</t>
+          <t>balance-30x25-tight-v6</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>4c7fb983c5d08f426c355de4a1f649169126cbfbac44f2a2fe4934d210ccff1d</t>
+          <t>9aa27138cff7db0cd33622795a3e82470ce02e0876586e743dbbb836a757c29a</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>9b20ee20036b73b0a32b1fdb4b502d199037c0e26fa748c50446de859a9d8369</t>
+          <t>0eb78c2d6be271b8e62d4a447ed874786b2c5dc31946df890f6d75ff93af61ae</t>
         </is>
       </c>
     </row>
